--- a/lead_generation_forms/042_property_innovation_hub_contact_form--lead_generation_forms.xlsx
+++ b/lead_generation_forms/042_property_innovation_hub_contact_form--lead_generation_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -780,8 +780,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -809,12 +809,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'residential',_'value':_'residential'}</t>
+          <t>residential</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Residential', 'value': 'residential'}</t>
+          <t>Residential</t>
         </is>
       </c>
     </row>
@@ -826,12 +826,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'commercial',_'value':_'commercial'}</t>
+          <t>commercial</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Commercial', 'value': 'commercial'}</t>
+          <t>Commercial</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'mixed',_'value':_'mixed'}</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Mixed', 'value': 'mixed'}</t>
+          <t>Mixed</t>
         </is>
       </c>
     </row>
@@ -860,12 +860,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'active',_'value':_'active'}</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Active', 'value': 'active'}</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -877,12 +877,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'inactive',_'value':_'inactive'}</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Inactive', 'value': 'inactive'}</t>
+          <t>Inactive</t>
         </is>
       </c>
     </row>
@@ -894,12 +894,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_6,_'label':_'under_construction',_'value':_'under_construction'}</t>
+          <t>under_construction</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 6, 'label': 'Under construction', 'value': 'under_construction'}</t>
+          <t>Under construction</t>
         </is>
       </c>
     </row>
@@ -911,12 +911,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_7,_'label':_'general_question',_'value':_'general_question'}</t>
+          <t>general_question</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 7, 'label': 'General question', 'value': 'general_question'}</t>
+          <t>General question</t>
         </is>
       </c>
     </row>
@@ -928,12 +928,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_8,_'label':_'request_for_information',_'value':_'request_for_information'}</t>
+          <t>request_for_information</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 8, 'label': 'Request for information', 'value': 'request_for_information'}</t>
+          <t>Request for information</t>
         </is>
       </c>
     </row>
@@ -945,12 +945,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_9,_'label':_'request_for_proposal',_'value':_'request_for_proposal'}</t>
+          <t>request_for_proposal</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 9, 'label': 'Request for proposal', 'value': 'request_for_proposal'}</t>
+          <t>Request for proposal</t>
         </is>
       </c>
     </row>
